--- a/data/00409A_20261008.xlsx
+++ b/data/00409A_20261008.xlsx
@@ -14,24 +14,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="252">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255">
   <x:si>
     <x:t>復華全球未來50主動式ETF基金（證劵代碼：00409A）</x:t>
   </x:si>
   <x:si>
-    <x:t>日期: 2026/10/07</x:t>
+    <x:t>日期: 2026/10/08</x:t>
   </x:si>
   <x:si>
     <x:t>基金資產淨值</x:t>
   </x:si>
   <x:si>
-    <x:t>14,358,540,115</x:t>
+    <x:t>13,951,773,902</x:t>
   </x:si>
   <x:si>
     <x:t>基金在外流通單位數</x:t>
   </x:si>
   <x:si>
-    <x:t>1,381,448,000</x:t>
+    <x:t>1,377,948,000</x:t>
   </x:si>
   <x:si>
     <x:t>基金每單位淨值</x:t>
@@ -61,10 +61,10 @@
     <x:t>25,500</x:t>
   </x:si>
   <x:si>
-    <x:t>903,403,240</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.292%</x:t>
+    <x:t>854,026,503</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.121%</x:t>
   </x:si>
   <x:si>
     <x:t>BE US</x:t>
@@ -76,10 +76,10 @@
     <x:t>85,000</x:t>
   </x:si>
   <x:si>
-    <x:t>789,486,200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.498%</x:t>
+    <x:t>740,655,828</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.309%</x:t>
   </x:si>
   <x:si>
     <x:t>PLTR US</x:t>
@@ -91,10 +91,10 @@
     <x:t>115,500</x:t>
   </x:si>
   <x:si>
-    <x:t>714,911,542</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.979%</x:t>
+    <x:t>733,290,376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.256%</x:t>
   </x:si>
   <x:si>
     <x:t>8046</x:t>
@@ -106,10 +106,10 @@
     <x:t>475,000</x:t>
   </x:si>
   <x:si>
-    <x:t>703,000,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.896%</x:t>
+    <x:t>700,625,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.022%</x:t>
   </x:si>
   <x:si>
     <x:t>3017</x:t>
@@ -121,10 +121,10 @@
     <x:t>173,000</x:t>
   </x:si>
   <x:si>
-    <x:t>613,285,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.271%</x:t>
+    <x:t>595,120,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.266%</x:t>
   </x:si>
   <x:si>
     <x:t>NVDA US</x:t>
@@ -136,10 +136,10 @@
     <x:t>80,000</x:t>
   </x:si>
   <x:si>
-    <x:t>605,757,474</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.219%</x:t>
+    <x:t>588,904,058</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.221%</x:t>
   </x:si>
   <x:si>
     <x:t>3026</x:t>
@@ -151,10 +151,10 @@
     <x:t>659,000</x:t>
   </x:si>
   <x:si>
-    <x:t>552,901,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.851%</x:t>
+    <x:t>577,943,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.142%</x:t>
   </x:si>
   <x:si>
     <x:t>MU US</x:t>
@@ -166,10 +166,145 @@
     <x:t>15,300</x:t>
   </x:si>
   <x:si>
-    <x:t>530,787,110</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.697%</x:t>
+    <x:t>506,180,515</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.628%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>景碩科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>454,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>488,050,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.498%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRWD US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crowdstrike控股公司</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>462,015,201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.312%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2383</x:t>
+  </x:si>
+  <x:si>
+    <x:t>台光電子</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>432,000,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.096%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3653</x:t>
+  </x:si>
+  <x:si>
+    <x:t>健策精密</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>415,570,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.979%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOOD US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>羅賓漢市場公司</x:t>
+  </x:si>
+  <x:si>
+    <x:t>110,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>375,957,163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.695%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSM US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>台灣積體電路製造股份有限公司</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>365,693,565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.621%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SPCX US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>太空探索科技公司</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>358,991,166</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.573%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRVL US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marvell Technology Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39,800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>349,140,156</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.502%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMD US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>超微半導體公司</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>317,182,376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.273%</x:t>
   </x:si>
   <x:si>
     <x:t>5274</x:t>
@@ -178,133 +313,13 @@
     <x:t>信驊科技</x:t>
   </x:si>
   <x:si>
-    <x:t>29,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>514,750,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.585%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>景碩科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>454,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>499,400,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.478%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRWD US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crowdstrike控股公司</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>465,510,091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.242%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3653</x:t>
-  </x:si>
-  <x:si>
-    <x:t>健策精密</x:t>
-  </x:si>
-  <x:si>
-    <x:t>58,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>394,690,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.749%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2383</x:t>
-  </x:si>
-  <x:si>
-    <x:t>台光電子</x:t>
-  </x:si>
-  <x:si>
-    <x:t>66,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>392,700,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.735%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOOD US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>羅賓漢市場公司</x:t>
-  </x:si>
-  <x:si>
-    <x:t>110,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>384,101,945</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.675%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSM US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>台灣積體電路製造股份有限公司</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>376,414,230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.622%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SPCX US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>太空探索科技公司</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>374,086,552</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.605%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRVL US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Marvell Technology Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>39,800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>361,276,798</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.516%</x:t>
+    <x:t>18,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>314,730,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.256%</x:t>
   </x:si>
   <x:si>
     <x:t>ALAB US</x:t>
@@ -316,25 +331,10 @@
     <x:t>28,000</x:t>
   </x:si>
   <x:si>
-    <x:t>341,275,858</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.377%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMD US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>超微半導體公司</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>329,502,271</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.295%</x:t>
+    <x:t>310,364,039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.225%</x:t>
   </x:si>
   <x:si>
     <x:t>AXTI US</x:t>
@@ -346,10 +346,25 @@
     <x:t>125,000</x:t>
   </x:si>
   <x:si>
-    <x:t>318,022,993</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.215%</x:t>
+    <x:t>286,093,593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.051%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELL US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>戴爾科技公司</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>275,258,287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.973%</x:t>
   </x:si>
   <x:si>
     <x:t>INTC US</x:t>
@@ -358,25 +373,25 @@
     <x:t>英特爾</x:t>
   </x:si>
   <x:si>
-    <x:t>288,555,546</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.010%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELL US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>戴爾科技公司</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>276,910,778</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.929%</x:t>
+    <x:t>273,602,250</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.961%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6976 JP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>太陽誘電</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>272,056,923</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.950%</x:t>
   </x:si>
   <x:si>
     <x:t>MSFT US</x:t>
@@ -385,25 +400,25 @@
     <x:t>微軟公司</x:t>
   </x:si>
   <x:si>
-    <x:t>253,378,910</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.765%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6976 JP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>太陽誘電</x:t>
-  </x:si>
-  <x:si>
-    <x:t>103,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>238,046,908</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.658%</x:t>
+    <x:t>250,374,612</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.795%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PANW US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Palo Alto Networks Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>232,916,754</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.669%</x:t>
   </x:si>
   <x:si>
     <x:t>2454</x:t>
@@ -415,25 +430,10 @@
     <x:t>49,000</x:t>
   </x:si>
   <x:si>
-    <x:t>236,915,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.650%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PANW US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Palo Alto Networks Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18,300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>236,655,692</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.648%</x:t>
+    <x:t>229,810,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.647%</x:t>
   </x:si>
   <x:si>
     <x:t>6787 JP</x:t>
@@ -445,10 +445,10 @@
     <x:t>43,500</x:t>
   </x:si>
   <x:si>
-    <x:t>235,983,827</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.644%</x:t>
+    <x:t>227,473,762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.630%</x:t>
   </x:si>
   <x:si>
     <x:t>6981 JP</x:t>
@@ -460,10 +460,55 @@
     <x:t>130,000</x:t>
   </x:si>
   <x:si>
-    <x:t>227,642,767</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.585%</x:t>
+    <x:t>216,986,931</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.555%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNOW US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Snowflake公司</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>213,873,126</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.533%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNDK US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>晟碟公司（德拉瓦州）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>205,618,172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.474%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NET US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cloudflare公司</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>197,645,207</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.417%</x:t>
   </x:si>
   <x:si>
     <x:t>6805</x:t>
@@ -472,73 +517,40 @@
     <x:t>富世達股</x:t>
   </x:si>
   <x:si>
-    <x:t>89,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>218,495,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.522%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNDK US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>晟碟公司（德拉瓦州）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>215,858,016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.503%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNOW US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Snowflake公司</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19,500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>206,958,474</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.441%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NET US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cloudflare公司</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18,100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>197,940,540</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.379%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMNR US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BitMine Immersion技術公司</x:t>
-  </x:si>
-  <x:si>
-    <x:t>200,640</x:t>
-  </x:si>
-  <x:si>
-    <x:t>157,764,990</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.099%</x:t>
+    <x:t>137,460,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.985%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRCX US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>科林研發股份有限公司</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>127,991,550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.917%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEHR US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>愛赫測試系統</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>125,343,009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.898%</x:t>
   </x:si>
   <x:si>
     <x:t>TSEM US</x:t>
@@ -550,40 +562,25 @@
     <x:t>17,000</x:t>
   </x:si>
   <x:si>
-    <x:t>134,566,892</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.937%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRCX US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>科林研發股份有限公司</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12,500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>131,334,448</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.915%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEHR US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>愛赫測試系統</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>128,234,332</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.893%</x:t>
+    <x:t>124,202,786</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.890%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6857 JP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>愛德萬測試</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>115,694,328</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.829%</x:t>
   </x:si>
   <x:si>
     <x:t>STM US</x:t>
@@ -595,10 +592,10 @@
     <x:t>63,000</x:t>
   </x:si>
   <x:si>
-    <x:t>112,855,395</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.786%</x:t>
+    <x:t>106,060,795</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.760%</x:t>
   </x:si>
   <x:si>
     <x:t>FORM US</x:t>
@@ -607,28 +604,25 @@
     <x:t>福達電子公司</x:t>
   </x:si>
   <x:si>
-    <x:t>18,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>80,237,930</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.559%</x:t>
+    <x:t>78,836,311</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.565%</x:t>
   </x:si>
   <x:si>
     <x:t>COHR US</x:t>
   </x:si>
   <x:si>
-    <x:t>連貫公司</x:t>
+    <x:t>高意公司</x:t>
   </x:si>
   <x:si>
     <x:t>6,300</x:t>
   </x:si>
   <x:si>
-    <x:t>67,207,015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.468%</x:t>
+    <x:t>60,837,567</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.436%</x:t>
   </x:si>
   <x:si>
     <x:t>NTRA US</x:t>
@@ -637,25 +631,10 @@
     <x:t>那提拉公司</x:t>
   </x:si>
   <x:si>
-    <x:t>50,451,305</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.351%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6857 JP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>愛德萬測試</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>49,961,657</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.348%</x:t>
+    <x:t>49,925,767</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.358%</x:t>
   </x:si>
   <x:si>
     <x:t>5801 JP</x:t>
@@ -667,10 +646,25 @@
     <x:t>50,000</x:t>
   </x:si>
   <x:si>
-    <x:t>44,811,013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.312%</x:t>
+    <x:t>42,601,486</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.305%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2308</x:t>
+  </x:si>
+  <x:si>
+    <x:t>台達電子</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39,300,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.282%</x:t>
   </x:si>
   <x:si>
     <x:t>NBIS US</x:t>
@@ -682,10 +676,10 @@
     <x:t>4,500</x:t>
   </x:si>
   <x:si>
-    <x:t>34,027,942</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.237%</x:t>
+    <x:t>31,577,930</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.226%</x:t>
   </x:si>
   <x:si>
     <x:t>TWLO US</x:t>
@@ -697,27 +691,42 @@
     <x:t>3,500</x:t>
   </x:si>
   <x:si>
-    <x:t>30,467,073</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.212%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IREN US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IREN有限公司</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24,673,387</x:t>
+    <x:t>30,827,363</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.221%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>愛惠浦公司</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,045,276</x:t>
   </x:si>
   <x:si>
     <x:t>0.172%</x:t>
   </x:si>
   <x:si>
+    <x:t>PSX US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>菲利普66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,379</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21,396,779</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.153%</x:t>
+  </x:si>
+  <x:si>
     <x:t>GOOGL US</x:t>
   </x:si>
   <x:si>
@@ -727,10 +736,10 @@
     <x:t>1,000</x:t>
   </x:si>
   <x:si>
-    <x:t>11,176,043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.078%</x:t>
+    <x:t>11,124,034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.080%</x:t>
   </x:si>
   <x:si>
     <x:t>AMZN US</x:t>
@@ -739,7 +748,7 @@
     <x:t>亞馬遜公司</x:t>
   </x:si>
   <x:si>
-    <x:t>8,287,809</x:t>
+    <x:t>8,114,422</x:t>
   </x:si>
   <x:si>
     <x:t>0.058%</x:t>
@@ -754,10 +763,10 @@
     <x:t>2,000</x:t>
   </x:si>
   <x:si>
-    <x:t>5,155,328</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.036%</x:t>
+    <x:t>5,163,898</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.037%</x:t>
   </x:si>
   <x:si>
     <x:t>NOW US</x:t>
@@ -766,10 +775,10 @@
     <x:t>ServiceNow公司</x:t>
   </x:si>
   <x:si>
-    <x:t>4,396,123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.031%</x:t>
+    <x:t>4,463,475</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.032%</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1178,7 +1187,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E60"/>
+  <x:dimension ref="A1:E61"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1226,7 +1235,7 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="3" t="n">
-        <x:v>10.39</x:v>
+        <x:v>10.13</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
@@ -1594,24 +1603,24 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="C32" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D32" s="6" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E32" s="6" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="5" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B33" s="4" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C33" s="6" t="s">
-        <x:v>118</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D33" s="6" t="s">
         <x:v>119</x:v>
@@ -1628,24 +1637,24 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="C34" s="6" t="s">
-        <x:v>118</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D34" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E34" s="6" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="5" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B35" s="4" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C35" s="6" t="s">
-        <x:v>127</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D35" s="6" t="s">
         <x:v>128</x:v>
@@ -1781,302 +1790,319 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="C43" s="6" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D43" s="6" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="D43" s="6" t="s">
+      <x:c r="E43" s="6" t="s">
         <x:v>168</x:v>
-      </x:c>
-      <x:c r="E43" s="6" t="s">
-        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="5" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B44" s="4" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="B44" s="4" t="s">
+      <x:c r="C44" s="6" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C44" s="6" t="s">
+      <x:c r="D44" s="6" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="D44" s="6" t="s">
+      <x:c r="E44" s="6" t="s">
         <x:v>173</x:v>
-      </x:c>
-      <x:c r="E44" s="6" t="s">
-        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="5" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B45" s="4" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="B45" s="4" t="s">
+      <x:c r="C45" s="6" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="C45" s="6" t="s">
+      <x:c r="D45" s="6" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="D45" s="6" t="s">
+      <x:c r="E45" s="6" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="E45" s="6" t="s">
-        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="5" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B46" s="4" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="B46" s="4" t="s">
+      <x:c r="C46" s="6" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="C46" s="6" t="s">
+      <x:c r="D46" s="6" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="D46" s="6" t="s">
+      <x:c r="E46" s="6" t="s">
         <x:v>183</x:v>
-      </x:c>
-      <x:c r="E46" s="6" t="s">
-        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="5" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B47" s="4" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="B47" s="4" t="s">
+      <x:c r="C47" s="6" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="C47" s="6" t="s">
+      <x:c r="D47" s="6" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="D47" s="6" t="s">
+      <x:c r="E47" s="6" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="E47" s="6" t="s">
-        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="5" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B48" s="4" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="B48" s="4" t="s">
+      <x:c r="C48" s="6" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="C48" s="6" t="s">
+      <x:c r="D48" s="6" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="D48" s="6" t="s">
+      <x:c r="E48" s="6" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="E48" s="6" t="s">
-        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="5" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B49" s="4" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="B49" s="4" t="s">
+      <x:c r="C49" s="6" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D49" s="6" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="C49" s="6" t="s">
+      <x:c r="E49" s="6" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="D49" s="6" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="E49" s="6" t="s">
-        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="5" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B50" s="4" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C50" s="6" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="B50" s="4" t="s">
+      <x:c r="D50" s="6" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="C50" s="6" t="s">
+      <x:c r="E50" s="6" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="D50" s="6" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="E50" s="6" t="s">
-        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="5" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B51" s="4" t="s">
-        <x:v>206</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C51" s="6" t="s">
         <x:v>157</x:v>
       </x:c>
       <x:c r="D51" s="6" t="s">
-        <x:v>207</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E51" s="6" t="s">
-        <x:v>208</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="5" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B52" s="4" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="C52" s="6" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="B52" s="4" t="s">
+      <x:c r="D52" s="6" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="C52" s="6" t="s">
+      <x:c r="E52" s="6" t="s">
         <x:v>211</x:v>
-      </x:c>
-      <x:c r="D52" s="6" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="E52" s="6" t="s">
-        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="5" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B53" s="4" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C53" s="6" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="B53" s="4" t="s">
+      <x:c r="D53" s="6" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="C53" s="6" t="s">
+      <x:c r="E53" s="6" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="D53" s="6" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="E53" s="6" t="s">
-        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="5" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B54" s="4" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C54" s="6" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="B54" s="4" t="s">
+      <x:c r="D54" s="6" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="C54" s="6" t="s">
+      <x:c r="E54" s="6" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="D54" s="6" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="E54" s="6" t="s">
-        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="5" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B55" s="4" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C55" s="6" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="B55" s="4" t="s">
+      <x:c r="D55" s="6" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="C55" s="6" t="s">
+      <x:c r="E55" s="6" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="D55" s="6" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="E55" s="6" t="s">
-        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="5" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B56" s="4" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="C56" s="6" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="B56" s="4" t="s">
+      <x:c r="D56" s="6" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="C56" s="6" t="s">
+      <x:c r="E56" s="6" t="s">
         <x:v>231</x:v>
-      </x:c>
-      <x:c r="D56" s="6" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="E56" s="6" t="s">
-        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="5" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B57" s="4" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C57" s="6" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="B57" s="4" t="s">
+      <x:c r="D57" s="6" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="C57" s="6" t="s">
+      <x:c r="E57" s="6" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="D57" s="6" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="E57" s="6" t="s">
-        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="5" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B58" s="4" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C58" s="6" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="B58" s="4" t="s">
+      <x:c r="D58" s="6" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="C58" s="6" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D58" s="6" t="s">
+      <x:c r="E58" s="6" t="s">
         <x:v>241</x:v>
-      </x:c>
-      <x:c r="E58" s="6" t="s">
-        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="5" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="B59" s="4" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="B59" s="4" t="s">
+      <x:c r="C59" s="6" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D59" s="6" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="C59" s="6" t="s">
+      <x:c r="E59" s="6" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="D59" s="6" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="E59" s="6" t="s">
-        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="5" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="B60" s="4" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="C60" s="6" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="B60" s="4" t="s">
+      <x:c r="D60" s="6" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="C60" s="6" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D60" s="6" t="s">
+      <x:c r="E60" s="6" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="E60" s="6" t="s">
+    </x:row>
+    <x:row r="61" spans="1:5">
+      <x:c r="A61" s="5" t="s">
         <x:v>251</x:v>
+      </x:c>
+      <x:c r="B61" s="4" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="C61" s="6" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D61" s="6" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="E61" s="6" t="s">
+        <x:v>254</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
